--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260807.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260807.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>149,185</t>
+          <t>144,685</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>29.95%</t>
+          <t>30.02%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>16,985</t>
+          <t>16,485</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.11%</t>
+          <t>7.91%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>108,120</t>
+          <t>104,820</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.40%</t>
+          <t>7.47%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>55,075</t>
+          <t>53,365</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.54%</t>
+          <t>5.66%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>131,445</t>
+          <t>127,295</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.31%</t>
+          <t>5.22%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>64,630</t>
+          <t>62,630</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.79%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>71,035</t>
+          <t>68,835</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>6,125</t>
+          <t>5,985</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>49,115</t>
+          <t>47,365</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>19,783</t>
+          <t>19,173</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
@@ -831,73 +831,73 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>21,425</t>
+          <t>20,725</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>83,505</t>
+          <t>180,043,801</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>34,260</t>
+          <t>80,705</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>21,995</t>
+          <t>33,160</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,39 +909,39 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>55,395</t>
+          <t>21,295</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>3,662,888</t>
+          <t>53,645</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>28,748</t>
+          <t>27,858</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>39,220</t>
+          <t>38,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1007,78 +1007,78 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>21,080</t>
+          <t>20,430</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>96,050,801</t>
+          <t>62,248</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>64,448</t>
+          <t>8,390</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>8,660</t>
+          <t>10,036</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
@@ -1095,34 +1095,34 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>23,018</t>
+          <t>22,308</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>10,336</t>
+          <t>133,375</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1139,56 +1139,56 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>12,591</t>
+          <t>12,201</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>137,645</t>
+          <t>19,255</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>19,905</t>
+          <t>20,517</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -1205,34 +1205,34 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>17,121</t>
+          <t>16,571</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>21,177</t>
+          <t>45,390</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1249,34 +1249,34 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>40,650</t>
+          <t>39,390</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>46,840</t>
+          <t>1,529,083</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.74%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>12,655</t>
+          <t>12,265</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>100,119,500</t>
+          <t>219,477,900</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>466,194</t>
+          <t>6,456,960</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
